--- a/VibeProject1/Assets/Table/Character/CharacterStats.xlsx
+++ b/VibeProject1/Assets/Table/Character/CharacterStats.xlsx
@@ -460,8 +460,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
       </c>
       <c r="B2" t="n">
         <v>100</v>
@@ -486,8 +488,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Archer</t>
+        </is>
       </c>
       <c r="B3" t="n">
         <v>70</v>
@@ -512,8 +516,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ShieldBearer</t>
+        </is>
       </c>
       <c r="B4" t="n">
         <v>150</v>
@@ -564,8 +570,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -574,8 +582,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Archer</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -584,8 +594,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ShieldBearer</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>

--- a/VibeProject1/Assets/Table/Character/CharacterStats.xlsx
+++ b/VibeProject1/Assets/Table/Character/CharacterStats.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="CharacterStats" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="CharacterStrings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MercenaryClassStrings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -425,122 +426,588 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>MaxHp</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Defense</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>MoveSpeed</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>AttackInterval</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>MoraleSyncRate</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>HireCost</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Warrior01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Warrior</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>100</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>20</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
       <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>1.5</v>
       </c>
-      <c r="H2" t="n">
-        <v>5</v>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Archer</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>70</v>
+          <t>Warrior02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>1.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ShieldBearer</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>150</v>
+          <t>Warrior03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
         <v>20</v>
       </c>
       <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Warrior04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Warrior05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Warrior</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Archer01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Archer</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>70</v>
+      </c>
+      <c r="D7" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Archer02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Archer</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>70</v>
+      </c>
+      <c r="D8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Archer03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Archer</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>70</v>
+      </c>
+      <c r="D9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Archer04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Archer</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>70</v>
+      </c>
+      <c r="D10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Archer05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Archer</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>70</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ShieldBearer01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ShieldBearer</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>150</v>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" t="n">
         <v>2.5</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G12" t="n">
         <v>1.5</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H12" t="n">
         <v>1.2</v>
       </c>
-      <c r="H4" t="n">
-        <v>3</v>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ShieldBearer02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ShieldBearer</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>150</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ShieldBearer03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ShieldBearer</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>150</v>
+      </c>
+      <c r="D14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ShieldBearer04</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ShieldBearer</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>150</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ShieldBearer05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ShieldBearer</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>150</v>
+      </c>
+      <c r="D16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -554,6 +1021,212 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Warrior01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>전사이름1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Warrior02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>전사이름2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Warrior03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>전사이름3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Warrior04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>전사이름4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Warrior05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>전사이름5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Archer01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>궁수이름1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Archer02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>궁수이름2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Archer03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>궁수이름3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Archer04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>궁수이름4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Archer05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>궁수이름5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ShieldBearer01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>방패병이름1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ShieldBearer02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>방패병이름2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ShieldBearer03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>방패병이름3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ShieldBearer04</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>방패병이름4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ShieldBearer05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>방패병이름5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
